--- a/data/export/2026-10-18-浦东35路.xlsx
+++ b/data/export/2026-10-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1603,1228 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-浦东35路.xlsx
+++ b/data/export/2026-10-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -743,32 +743,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>115分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,17 +804,17 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -820,13 +824,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -887,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +945,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -998,7 +1006,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1056,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1117,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1167,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1228,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1278,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1339,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1389,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1450,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1500,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1561,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1611,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1672,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1722,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1783,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1833,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1894,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1944,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2005,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2055,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2116,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2166,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2227,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2277,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2338,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2388,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2449,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2499,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2560,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2610,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2671,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2721,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2721,22 +2729,22 @@
       <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2769,12 +2777,12 @@
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2788,7 +2796,7 @@
       <c r="T21" s="2" t="inlineStr"/>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2824,7 +2832,562 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-浦东35路.xlsx
+++ b/data/export/2026-10-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -753,19 +761,19 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>115分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -780,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -862,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -895,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -919,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -939,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1056,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1084,32 +1100,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1117,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1141,33 +1161,37 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1278,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1389,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1500,7 +1524,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1611,7 +1635,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1722,7 +1746,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1807,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1833,7 +1857,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1918,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1944,7 +1968,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2029,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2055,7 +2079,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2140,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2166,7 +2190,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2251,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2277,7 +2301,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2362,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2388,7 +2412,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2473,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2499,7 +2523,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2584,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2610,7 +2634,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2695,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2721,7 +2745,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2806,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2832,7 +2856,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2917,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2943,7 +2967,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3028,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3054,7 +3078,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3139,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3165,7 +3189,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3250,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3276,7 +3300,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3284,22 +3308,22 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3337,7 +3361,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3351,7 +3375,7 @@
       <c r="T26" s="2" t="inlineStr"/>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3387,7 +3411,574 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-浦东35路.xlsx
+++ b/data/export/2026-10-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,10 +446,10 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -880,24 +880,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -989,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1118,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -1137,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1186,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1252,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1276,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -1330,32 +1346,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1363,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1387,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1441,32 +1465,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1474,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1498,33 +1526,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1552,32 +1584,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1585,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1609,33 +1645,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1663,32 +1703,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1696,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1720,17 +1764,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1740,13 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1774,32 +1822,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1807,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1831,33 +1883,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1941,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq55，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1918,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1926,10 +1982,18 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
       <c r="R13" s="2" t="inlineStr"/>
       <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq22映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -1968,7 +2032,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2079,7 +2143,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2107,32 +2171,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2140,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2164,33 +2232,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2290,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq55，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2251,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2259,10 +2331,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2301,7 +2389,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2412,7 +2500,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2523,7 +2611,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2634,7 +2722,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2745,7 +2833,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2856,7 +2944,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2917,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2967,7 +3055,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3116,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3078,7 +3166,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3227,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3189,7 +3277,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3338,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3300,7 +3388,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3449,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3411,7 +3499,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3560,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3522,7 +3610,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3671,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3637,7 +3725,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3786,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3752,7 +3840,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3901,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3863,7 +3951,7 @@
       <c r="AB30" s="2" t="inlineStr"/>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3871,22 +3959,22 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -3924,7 +4012,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3973,12 +4061,1043 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A92076D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-浦东35路.xlsx
+++ b/data/export/2026-10-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC40"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>126.0</t>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq55，推进17站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq63，推进25站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2417,32 +2417,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2450,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2474,33 +2478,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2528,32 +2536,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2561,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2585,33 +2597,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -2639,32 +2655,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2672,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2696,33 +2716,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2822,7 +2846,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2861,32 +2885,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -2894,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2918,33 +2946,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2972,32 +3004,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -3005,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3029,33 +3065,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3083,32 +3123,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3116,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3140,17 +3184,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3160,13 +3204,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3194,32 +3242,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3227,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3251,17 +3303,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3271,13 +3323,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3305,32 +3361,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -3338,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3362,17 +3422,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3382,13 +3442,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3560,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3725,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3840,7 +3904,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4012,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4066,7 +4130,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4127,7 +4191,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4242,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4296,7 +4360,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4357,7 +4421,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4411,7 +4475,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4536,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4587,7 +4651,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4641,7 +4705,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4766,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4813,7 +4877,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4867,7 +4931,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4992,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4982,7 +5046,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4990,22 +5054,22 @@
       <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5038,12 +5102,12 @@
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5092,12 +5156,924 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
           <t>128.0</t>
         </is>
       </c>
-      <c r="AC40" s="2" t="inlineStr">
-        <is>
-          <t>6/28</t>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-浦东35路.xlsx
+++ b/data/export/2026-10-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3252,24 +3252,24 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3480,32 +3480,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3513,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3537,17 +3541,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3557,13 +3561,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3591,32 +3599,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3624,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3648,33 +3660,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3702,32 +3718,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3735,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3759,37 +3779,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3817,32 +3837,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3850,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3874,17 +3898,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3894,17 +3918,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,7 +4028,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4043,32 +4067,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4076,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4100,17 +4128,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4120,17 +4148,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4158,32 +4186,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4191,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4215,37 +4247,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4273,32 +4305,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4306,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4330,37 +4366,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4475,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4503,32 +4539,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4536,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4560,17 +4600,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4580,17 +4620,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4690,7 +4730,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4705,7 +4745,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4733,12 +4773,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq50，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4766,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4774,10 +4814,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr"/>
-      <c r="S37" s="2" t="inlineStr"/>
-      <c r="T37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq38（站名待映射） ETA 6分钟参与校验</t>
+        </is>
+      </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
           <t>09:38</t>
@@ -4877,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4931,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4992,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5046,7 +5102,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5161,7 +5217,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5276,7 +5332,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5393,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5448,7 +5504,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5502,7 +5558,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5678,7 +5734,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5732,7 +5788,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -5793,7 +5849,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5904,7 +5960,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5958,7 +6014,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6019,7 +6075,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6073,7 +6129,808 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>16/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-浦东35路.xlsx
+++ b/data/export/2026-10-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,12 +1784,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,18 +2132,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,17 +2256,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2378,7 +2382,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2454,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,17 +2502,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,17 +2621,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2807,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2846,7 +2850,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2922,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2976,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3095,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3218,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3337,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3571,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3755,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3928,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4158,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4277,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4576,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4658,32 +4662,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4691,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4715,17 +4723,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4735,17 +4743,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4786,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq50，推进12站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq60，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4806,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4861,7 +4869,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4900,32 +4908,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4933,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4957,37 +4969,37 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5130,32 +5142,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5163,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5187,17 +5203,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5207,12 +5223,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5245,32 +5261,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5278,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5302,17 +5322,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5322,17 +5342,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5360,32 +5380,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5393,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5417,33 +5441,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -5471,32 +5499,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5504,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5528,17 +5560,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5548,17 +5580,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5586,32 +5618,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5619,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5643,17 +5679,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5663,17 +5699,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5849,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5888,7 +5924,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5960,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6014,7 +6050,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6129,7 +6165,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6305,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6420,7 +6456,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6535,7 +6571,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6589,7 +6625,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6686,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6761,7 +6797,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6876,7 +6912,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6920,17 +6956,691 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A92076D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>16/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB55" s="2" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>7/28</t>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-浦东35路.xlsx
+++ b/data/export/2026-10-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2740,17 +2740,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2965,22 +2965,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3089,17 +3089,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3203,14 +3203,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3679,22 +3679,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5737,32 +5737,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5770,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5794,17 +5798,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5814,17 +5818,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5963,32 +5967,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -5996,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6020,37 +6028,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -6078,32 +6086,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -6111,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6135,17 +6147,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6155,17 +6167,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -6193,32 +6205,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -6226,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6250,17 +6266,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6270,12 +6286,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6308,32 +6324,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6341,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6365,37 +6385,37 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6495,7 +6515,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6510,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6538,32 +6558,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6571,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6595,17 +6619,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6615,17 +6639,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6797,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6851,7 +6875,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6966,7 +6990,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7027,7 +7051,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7138,7 +7162,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7192,7 +7216,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -7253,7 +7277,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7364,7 +7388,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7479,7 +7503,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7590,7 +7614,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7644,6 +7668,581 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>20/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-18-浦东35路.xlsx
+++ b/data/export/2026-10-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC66"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>133.5</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2021,18 +2021,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2327,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2512,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2811,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2926,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3164,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3337,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3579,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3759,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3803,17 +3807,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,14 +3921,14 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>133.5</t>
@@ -3932,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4227,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4266,17 +4270,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4346,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4390,17 +4394,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,7 +4504,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4515,7 +4519,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,22 +4742,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4945,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5114,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5536,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5709,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6004,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6361,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6443,32 +6447,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6476,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6500,17 +6508,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6520,17 +6528,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -6568,12 +6576,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -6595,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6634,17 +6642,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6710,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6788,32 +6796,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6821,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6845,17 +6857,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6865,17 +6877,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -6903,32 +6915,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -6936,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6960,37 +6976,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -7018,12 +7034,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq54，推进16站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7051,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7059,10 +7075,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q56" s="2" t="inlineStr"/>
-      <c r="R56" s="2" t="inlineStr"/>
-      <c r="S56" s="2" t="inlineStr"/>
-      <c r="T56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq38（站名待映射） ETA 29分钟参与校验</t>
+        </is>
+      </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
           <t>12:28</t>
@@ -7162,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7244,32 +7276,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7277,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7301,33 +7337,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -7388,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7503,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7614,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7725,7 +7765,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7840,7 +7880,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7955,7 +7995,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7999,17 +8039,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8110,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8185,7 +8225,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8243,6 +8283,581 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>22/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>20/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-18-浦东35路.xlsx
+++ b/data/export/2026-10-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AC76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,14 +2255,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>131.0</t>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2386,18 +2386,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2625,17 +2629,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2758,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2859,13 +2863,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2984,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3222,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,14 +3572,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>134.0</t>
@@ -3579,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3698,7 +3706,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3817,7 +3825,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3936,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4404,7 +4412,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4519,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4757,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4873,7 +4881,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4949,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4993,17 +5001,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,7 +5111,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5118,7 +5126,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5341,14 +5349,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>131.0</t>
@@ -5356,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5465,17 +5473,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5584,17 +5592,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5721,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5840,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5937,13 +5945,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6062,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6419,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6538,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6887,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7006,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7051,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq54，推进16站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq59，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7067,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7122,7 +7134,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7161,32 +7173,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -7194,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7218,17 +7234,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7238,17 +7254,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -7286,24 +7302,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7313,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7362,12 +7378,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -7395,32 +7411,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7428,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7452,17 +7472,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7472,17 +7492,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -7510,32 +7530,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7543,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7567,33 +7591,37 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -7621,32 +7649,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -7654,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7678,17 +7710,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7698,13 +7730,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB61" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -7732,32 +7768,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7765,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7789,17 +7829,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7809,17 +7849,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7934,7 +7974,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -7995,7 +8035,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8049,7 +8089,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8164,7 +8204,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -8225,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8279,7 +8319,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -8340,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8455,7 +8495,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8509,7 +8549,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -8570,7 +8610,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8624,7 +8664,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -8685,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8739,7 +8779,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -8747,22 +8787,22 @@
       <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A92076D</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8795,12 +8835,12 @@
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8814,47 +8854,618 @@
       <c r="T71" s="2" t="inlineStr"/>
       <c r="U71" s="2" t="inlineStr">
         <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
           <t>15:25</t>
         </is>
       </c>
-      <c r="V71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W71" s="2" t="inlineStr">
+      <c r="W72" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X71" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y71" s="2" t="inlineStr">
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z71" s="2" t="inlineStr">
+      <c r="Z72" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
+      <c r="AA72" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>24/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>25/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
         <is>
           <t>131.0</t>
         </is>
       </c>
-      <c r="AC71" s="2" t="inlineStr">
-        <is>
-          <t>14/28</t>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-浦东35路.xlsx
+++ b/data/export/2026-10-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC76"/>
+  <dimension ref="A1:AC84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2977,22 +2977,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3696,17 +3696,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3815,17 +3815,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4283,17 +4283,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,22 +6059,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6421,17 +6421,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6540,17 +6540,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6659,17 +6659,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -7778,24 +7778,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7887,32 +7887,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7920,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7944,17 +7948,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7964,17 +7968,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -8002,32 +8006,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8035,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8059,17 +8067,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8079,17 +8087,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -8117,32 +8125,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8150,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8174,17 +8186,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8194,17 +8206,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -8232,32 +8244,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -8265,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8289,37 +8305,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -8347,32 +8363,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8380,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8404,17 +8424,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8424,17 +8444,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8515,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8549,7 +8569,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -8610,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8725,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8779,7 +8799,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -8840,7 +8860,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8951,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9066,7 +9086,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9120,7 +9140,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9235,7 +9255,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9316,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9350,7 +9370,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9431,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9469,6 +9489,922 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>126.5</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>16/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>126.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr"/>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>130.7</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>24/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-18-浦东35路.xlsx
+++ b/data/export/2026-10-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC84"/>
+  <dimension ref="A1:AC92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,14 +1541,14 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
           <t>132.3</t>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>131.5</t>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3929,22 +3929,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4512,22 +4512,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4755,17 +4755,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4996,14 +4996,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>132.3</t>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5116,17 +5116,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6178,14 +6178,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>131.5</t>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7008,17 +7008,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7249,14 +7249,14 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
           <t>132.3</t>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8482,32 +8482,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8515,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8539,37 +8543,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -8597,32 +8601,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -8630,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8654,17 +8662,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8674,17 +8682,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -8712,32 +8720,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8745,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8769,37 +8781,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -8827,12 +8839,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq62，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8860,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8868,10 +8880,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q71" s="2" t="inlineStr"/>
-      <c r="R71" s="2" t="inlineStr"/>
-      <c r="S71" s="2" t="inlineStr"/>
-      <c r="T71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq38（站名待映射） ETA 5分钟参与校验</t>
+        </is>
+      </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
           <t>15:22</t>
@@ -8971,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9010,7 +9038,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9025,7 +9053,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -9053,32 +9081,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9086,7 +9118,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9110,17 +9142,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9130,17 +9162,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -9201,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9255,7 +9287,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -9316,7 +9348,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9370,7 +9402,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9485,7 +9517,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9661,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9715,7 +9747,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9891,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10006,7 +10038,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10121,7 +10153,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10232,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10286,7 +10318,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -10347,7 +10379,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10401,7 +10433,927 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>23/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>132.3</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>20/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>137.7</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>25/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-浦东35路.xlsx
+++ b/data/export/2026-10-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC92"/>
+  <dimension ref="A1:AC98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2391,17 +2391,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>127.3</t>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2748,17 +2748,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3215,14 +3215,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>131.5</t>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3572,22 +3572,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,22 +4159,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5354,17 +5354,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5587,14 +5587,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>127.3</t>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5830,17 +5830,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7611,17 +7611,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7844,14 +7844,14 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
           <t>127.3</t>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7963,14 +7963,14 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
           <t>131.5</t>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8692,7 +8692,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -9091,24 +9091,24 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -9200,32 +9200,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9233,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9257,37 +9261,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -9315,32 +9319,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9348,7 +9356,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9372,17 +9380,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9392,17 +9400,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -9430,32 +9438,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9463,7 +9475,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9487,17 +9499,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9507,17 +9519,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -9545,32 +9557,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9578,7 +9594,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9602,37 +9618,37 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -9660,32 +9676,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9693,7 +9713,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9717,17 +9737,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9737,17 +9757,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -9808,7 +9828,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9862,7 +9882,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9962,7 +9982,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -10038,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10153,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10264,7 +10284,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10379,7 +10399,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10494,7 +10514,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10548,7 +10568,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -10609,7 +10629,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10724,7 +10744,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10839,7 +10859,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10893,7 +10913,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10974,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11069,7 +11089,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11184,7 +11204,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11238,7 +11258,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -11246,22 +11266,22 @@
       <c r="A92" s="2" t="inlineStr"/>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A92076D</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>18:25</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -11294,12 +11314,12 @@
       <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11313,47 +11333,733 @@
       <c r="T92" s="2" t="inlineStr"/>
       <c r="U92" s="2" t="inlineStr">
         <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr"/>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
           <t>18:25</t>
         </is>
       </c>
-      <c r="V92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W92" s="2" t="inlineStr">
+      <c r="W93" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X92" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y92" s="2" t="inlineStr">
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z92" s="2" t="inlineStr">
+      <c r="Z93" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA92" s="2" t="inlineStr">
+      <c r="AA93" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB92" s="2" t="inlineStr">
+      <c r="AB93" s="2" t="inlineStr">
         <is>
           <t>131.5</t>
         </is>
       </c>
-      <c r="AC92" s="2" t="inlineStr">
-        <is>
-          <t>15/28</t>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>127.3</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>127.3</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-浦东35路.xlsx
+++ b/data/export/2026-10-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC98"/>
+  <dimension ref="A1:AC105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,14 +2255,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2743,22 +2743,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2982,17 +2982,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>26/28</t>
+          <t>27/28</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3458,12 +3458,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3934,17 +3934,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4044,18 +4044,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB30" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4174,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4297,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4402,17 +4406,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4527,7 +4531,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,22 +4635,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4957,7 +4961,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5011,7 +5015,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5111,7 +5115,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5126,7 +5130,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5230,22 +5234,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5349,14 +5353,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -5364,7 +5368,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5433,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5483,7 +5487,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5552,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5602,7 +5606,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5825,22 +5829,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6020,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6064,17 +6068,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6193,7 +6197,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6302,12 +6306,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6431,7 +6435,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6669,7 +6673,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6769,18 +6773,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB53" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6889,17 +6897,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7210,7 +7218,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7264,7 +7272,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7383,7 +7391,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7502,7 +7510,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7606,7 +7614,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7686,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7805,7 +7813,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7859,7 +7867,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7932,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7978,7 +7986,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8224,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8289,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8325,17 +8333,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -8454,7 +8462,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8527,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8563,17 +8571,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -8692,7 +8700,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8765,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8811,7 +8819,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8880,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8999,7 +9007,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9053,7 +9061,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9126,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9157,7 +9165,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9172,7 +9180,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -9237,7 +9245,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9291,7 +9299,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9364,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9395,7 +9403,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9475,7 +9483,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9514,14 +9522,14 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -9529,7 +9537,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -9594,7 +9602,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9648,7 +9656,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -9686,24 +9694,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9713,7 +9721,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9752,22 +9760,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -9795,32 +9803,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -9828,7 +9840,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9852,37 +9864,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -9910,32 +9922,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9943,7 +9959,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9967,17 +9983,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9987,12 +10003,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10025,32 +10041,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10058,7 +10078,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10082,37 +10102,37 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -10140,32 +10160,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -10173,7 +10197,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10197,33 +10221,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB82" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -10251,32 +10279,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10284,7 +10316,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10308,17 +10340,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10328,17 +10360,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -10366,32 +10398,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -10399,7 +10435,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10423,17 +10459,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10443,17 +10479,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10550,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10568,7 +10604,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -10711,32 +10747,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10744,7 +10784,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10768,17 +10808,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10788,17 +10828,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -10859,7 +10899,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10913,7 +10953,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -10974,7 +11014,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11089,7 +11129,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11143,7 +11183,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -11204,7 +11244,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11258,7 +11298,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -11319,7 +11359,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11430,7 +11470,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11484,7 +11524,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -11545,7 +11585,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11599,7 +11639,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11700,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11714,7 +11754,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -11775,7 +11815,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11829,7 +11869,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -11847,7 +11887,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -11890,7 +11930,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11904,7 +11944,7 @@
       <c r="T97" s="2" t="inlineStr"/>
       <c r="U97" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="V97" s="2" t="inlineStr">
@@ -11934,12 +11974,12 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
@@ -12005,7 +12045,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12059,7 +12099,812 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>22/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>24/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>133.3</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>23/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>129.3</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-浦东35路.xlsx
+++ b/data/export/2026-10-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC105"/>
+  <dimension ref="A1:AC107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3096,22 +3096,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3577,17 +3577,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6182,22 +6182,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7976,12 +7976,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
@@ -8819,7 +8819,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9245,7 +9245,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9289,17 +9289,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -9364,7 +9364,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -10604,7 +10604,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11096,32 +11096,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11129,7 +11133,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11153,17 +11157,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11173,7 +11177,7 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
@@ -11183,7 +11187,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -11244,7 +11248,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11298,7 +11302,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -11326,12 +11330,12 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq57，推进19站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -11359,7 +11363,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11367,10 +11371,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q92" s="2" t="inlineStr"/>
-      <c r="R92" s="2" t="inlineStr"/>
-      <c r="S92" s="2" t="inlineStr"/>
-      <c r="T92" s="2" t="inlineStr"/>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>19:08</t>
+        </is>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
+          <t>19:14</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±6分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U92" s="2" t="inlineStr">
         <is>
           <t>18:12</t>
@@ -11437,32 +11457,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11470,7 +11494,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11494,37 +11518,37 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA93" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -11552,32 +11576,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11585,7 +11613,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11609,17 +11637,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11629,12 +11657,12 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11667,32 +11695,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11700,7 +11732,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11724,17 +11756,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11744,17 +11776,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -11815,7 +11847,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11930,7 +11962,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12045,7 +12077,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12160,7 +12192,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12275,7 +12307,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12329,7 +12361,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12422,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12505,7 +12537,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12620,7 +12652,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12674,7 +12706,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -12735,7 +12767,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12850,7 +12882,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12908,6 +12940,236 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-18-浦东35路.xlsx
+++ b/data/export/2026-10-18-浦东35路.xlsx
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2629,17 +2629,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3225,12 +3225,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4168,17 +4168,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5120,17 +5120,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5358,17 +5358,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5596,17 +5596,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7857,17 +7857,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -9061,7 +9061,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9170,17 +9170,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9527,17 +9527,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9646,17 +9646,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -10604,7 +10604,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -11187,7 +11187,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -11302,7 +11302,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -11467,24 +11467,24 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11543,12 +11543,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -11586,24 +11586,24 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -11613,7 +11613,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -11717,12 +11717,12 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11814,32 +11814,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11847,7 +11851,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11871,17 +11875,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11891,17 +11895,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -11962,7 +11966,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12044,32 +12048,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12077,7 +12085,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12101,17 +12109,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12121,17 +12129,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -12159,32 +12167,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -12192,7 +12204,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12216,17 +12228,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12236,17 +12248,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -12274,12 +12286,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq52，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -12307,7 +12319,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12315,10 +12327,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q100" s="2" t="inlineStr"/>
-      <c r="R100" s="2" t="inlineStr"/>
-      <c r="S100" s="2" t="inlineStr"/>
-      <c r="T100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>20:16</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U100" s="2" t="inlineStr">
         <is>
           <t>19:20</t>
@@ -12361,7 +12389,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -12422,7 +12450,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12537,7 +12565,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12619,32 +12647,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:43</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -12652,7 +12684,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12676,17 +12708,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12696,17 +12728,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -12767,7 +12799,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12882,7 +12914,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12997,7 +13029,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13112,7 +13144,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13161,12 +13193,12 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-18-浦东35路.xlsx
+++ b/data/export/2026-10-18-浦东35路.xlsx
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>129.8</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2748,17 +2748,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5239,17 +5239,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>129.8</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5834,17 +5834,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -9483,7 +9483,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9532,12 +9532,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>129.8</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9765,17 +9765,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10122,17 +10122,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -11905,7 +11905,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -12291,7 +12291,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq52，推进24站，达到≥2站确认条件</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12532,32 +12532,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -12565,7 +12569,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12589,17 +12593,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12609,12 +12613,12 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
@@ -12657,24 +12661,24 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -12684,7 +12688,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12733,12 +12737,12 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>129.8</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -12766,32 +12770,36 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -12799,7 +12807,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12823,17 +12831,17 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
@@ -12843,17 +12851,17 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -12881,32 +12889,36 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12914,7 +12926,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12938,17 +12950,17 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
@@ -12958,17 +12970,17 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -13029,7 +13041,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13144,7 +13156,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
